--- a/Assets/Lion/Ally/Data/Excel/Ally_4.xlsx
+++ b/Assets/Lion/Ally/Data/Excel/Ally_4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vantan\Lion\Assets\Lion\Ally\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vantan\Lion\Assets\Lion\Ally\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E624FEB3-B740-4A79-BD2E-0F53755C1FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E311A56-D33A-4D6F-8AFE-322B7E74DA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ExpLevelStatusTable" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="12">
   <si>
     <t>Level</t>
     <phoneticPr fontId="1"/>
@@ -69,6 +69,10 @@
   </si>
   <si>
     <t>HP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AvailableMinionsCount</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -423,9 +427,10 @@
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
     <col min="3" max="7" width="9" style="2"/>
+    <col min="10" max="10" width="22.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -453,8 +458,11 @@
       <c r="I1" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>1</v>
       </c>
@@ -482,8 +490,11 @@
       <c r="I2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -511,8 +522,11 @@
       <c r="I3">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>3</v>
       </c>
@@ -540,8 +554,11 @@
       <c r="I4">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="J4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>4</v>
       </c>
@@ -569,8 +586,11 @@
       <c r="I5">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="J5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -598,8 +618,11 @@
       <c r="I6">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="J6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>6</v>
       </c>
@@ -627,8 +650,11 @@
       <c r="I7">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="J7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>7</v>
       </c>
@@ -656,8 +682,11 @@
       <c r="I8">
         <v>1.6</v>
       </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="J8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -685,8 +714,11 @@
       <c r="I9">
         <v>1.7</v>
       </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="J9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>9</v>
       </c>
@@ -714,8 +746,11 @@
       <c r="I10">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="J10" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>10</v>
       </c>
@@ -743,8 +778,11 @@
       <c r="I11">
         <v>1.9</v>
       </c>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="J11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -772,8 +810,11 @@
       <c r="I12">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="J12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13">
         <v>12</v>
       </c>
@@ -801,8 +842,11 @@
       <c r="I13">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="J13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>13</v>
       </c>
@@ -830,8 +874,11 @@
       <c r="I14">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="J14" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -859,8 +906,11 @@
       <c r="I15">
         <v>2.2999999999999998</v>
       </c>
-    </row>
-    <row r="16" spans="1:9">
+      <c r="J15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16">
         <v>15</v>
       </c>
@@ -888,8 +938,11 @@
       <c r="I16">
         <v>2.4</v>
       </c>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="J16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17">
         <v>16</v>
       </c>
@@ -917,8 +970,11 @@
       <c r="I17">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="J17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -946,8 +1002,11 @@
       <c r="I18">
         <v>2.6</v>
       </c>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="J18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19">
         <v>18</v>
       </c>
@@ -975,8 +1034,11 @@
       <c r="I19">
         <v>2.7</v>
       </c>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="J19" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1004,8 +1066,11 @@
       <c r="I20">
         <v>2.8</v>
       </c>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="J20" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1033,8 +1098,11 @@
       <c r="I21">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="J21" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1062,8 +1130,11 @@
       <c r="I22">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:9">
+      <c r="J22" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1091,8 +1162,11 @@
       <c r="I23">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="J23" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1120,8 +1194,11 @@
       <c r="I24">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="25" spans="1:9">
+      <c r="J24" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1149,8 +1226,11 @@
       <c r="I25">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="26" spans="1:9">
+      <c r="J25" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1178,8 +1258,11 @@
       <c r="I26">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="27" spans="1:9">
+      <c r="J26" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1207,8 +1290,11 @@
       <c r="I27">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="28" spans="1:9">
+      <c r="J27" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1236,8 +1322,11 @@
       <c r="I28">
         <v>3.6</v>
       </c>
-    </row>
-    <row r="29" spans="1:9">
+      <c r="J28" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1265,8 +1354,11 @@
       <c r="I29">
         <v>3.7</v>
       </c>
-    </row>
-    <row r="30" spans="1:9">
+      <c r="J29" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1294,8 +1386,11 @@
       <c r="I30">
         <v>3.8</v>
       </c>
-    </row>
-    <row r="31" spans="1:9">
+      <c r="J30" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1323,8 +1418,11 @@
       <c r="I31">
         <v>3.9</v>
       </c>
-    </row>
-    <row r="32" spans="1:9">
+      <c r="J31" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1352,8 +1450,11 @@
       <c r="I32">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="1:9">
+      <c r="J32" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1381,8 +1482,11 @@
       <c r="I33">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="34" spans="1:9">
+      <c r="J33" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1410,8 +1514,11 @@
       <c r="I34">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="35" spans="1:9">
+      <c r="J34" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1439,8 +1546,11 @@
       <c r="I35">
         <v>4.3</v>
       </c>
-    </row>
-    <row r="36" spans="1:9">
+      <c r="J35" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1468,8 +1578,11 @@
       <c r="I36">
         <v>4.4000000000000004</v>
       </c>
-    </row>
-    <row r="37" spans="1:9">
+      <c r="J36" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1497,8 +1610,11 @@
       <c r="I37">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="38" spans="1:9">
+      <c r="J37" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1526,8 +1642,11 @@
       <c r="I38">
         <v>4.5999999999999996</v>
       </c>
-    </row>
-    <row r="39" spans="1:9">
+      <c r="J38" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1555,8 +1674,11 @@
       <c r="I39">
         <v>4.7</v>
       </c>
-    </row>
-    <row r="40" spans="1:9">
+      <c r="J39" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1584,8 +1706,11 @@
       <c r="I40">
         <v>4.8</v>
       </c>
-    </row>
-    <row r="41" spans="1:9">
+      <c r="J40" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1613,8 +1738,11 @@
       <c r="I41">
         <v>4.9000000000000004</v>
       </c>
-    </row>
-    <row r="42" spans="1:9">
+      <c r="J41" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1642,8 +1770,11 @@
       <c r="I42">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="1:9">
+      <c r="J42" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -1671,8 +1802,11 @@
       <c r="I43">
         <v>5.0999999999999996</v>
       </c>
-    </row>
-    <row r="44" spans="1:9">
+      <c r="J43" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1700,8 +1834,11 @@
       <c r="I44">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="45" spans="1:9">
+      <c r="J44" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1729,8 +1866,11 @@
       <c r="I45">
         <v>5.3</v>
       </c>
-    </row>
-    <row r="46" spans="1:9">
+      <c r="J45" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1758,8 +1898,11 @@
       <c r="I46">
         <v>5.4</v>
       </c>
-    </row>
-    <row r="47" spans="1:9">
+      <c r="J46" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -1787,8 +1930,11 @@
       <c r="I47">
         <v>5.5</v>
       </c>
-    </row>
-    <row r="48" spans="1:9">
+      <c r="J47" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1816,8 +1962,11 @@
       <c r="I48">
         <v>5.6</v>
       </c>
-    </row>
-    <row r="49" spans="1:9">
+      <c r="J48" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1845,8 +1994,11 @@
       <c r="I49">
         <v>5.7</v>
       </c>
-    </row>
-    <row r="50" spans="1:9">
+      <c r="J49" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -1874,8 +2026,11 @@
       <c r="I50">
         <v>5.8</v>
       </c>
-    </row>
-    <row r="51" spans="1:9">
+      <c r="J50" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1903,8 +2058,11 @@
       <c r="I51">
         <v>5.9</v>
       </c>
-    </row>
-    <row r="52" spans="1:9">
+      <c r="J51" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1932,8 +2090,11 @@
       <c r="I52">
         <v>6</v>
       </c>
-    </row>
-    <row r="53" spans="1:9">
+      <c r="J52" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -1961,8 +2122,11 @@
       <c r="I53">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="54" spans="1:9">
+      <c r="J53" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1990,8 +2154,11 @@
       <c r="I54">
         <v>6.2</v>
       </c>
-    </row>
-    <row r="55" spans="1:9">
+      <c r="J54" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2019,8 +2186,11 @@
       <c r="I55">
         <v>6.3</v>
       </c>
-    </row>
-    <row r="56" spans="1:9">
+      <c r="J55" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -2048,8 +2218,11 @@
       <c r="I56">
         <v>6.4</v>
       </c>
-    </row>
-    <row r="57" spans="1:9">
+      <c r="J56" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2077,8 +2250,11 @@
       <c r="I57">
         <v>6.5000000000000098</v>
       </c>
-    </row>
-    <row r="58" spans="1:9">
+      <c r="J57" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2106,8 +2282,11 @@
       <c r="I58">
         <v>6.6</v>
       </c>
-    </row>
-    <row r="59" spans="1:9">
+      <c r="J58" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -2135,8 +2314,11 @@
       <c r="I59">
         <v>6.7</v>
       </c>
-    </row>
-    <row r="60" spans="1:9">
+      <c r="J59" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2164,8 +2346,11 @@
       <c r="I60">
         <v>6.8000000000000096</v>
       </c>
-    </row>
-    <row r="61" spans="1:9">
+      <c r="J60" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2193,8 +2378,11 @@
       <c r="I61">
         <v>6.9000000000000101</v>
       </c>
-    </row>
-    <row r="62" spans="1:9">
+      <c r="J61" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -2222,8 +2410,11 @@
       <c r="I62">
         <v>7.0000000000000098</v>
       </c>
-    </row>
-    <row r="63" spans="1:9">
+      <c r="J62" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2251,8 +2442,11 @@
       <c r="I63">
         <v>7.1</v>
       </c>
-    </row>
-    <row r="64" spans="1:9">
+      <c r="J63" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2280,8 +2474,11 @@
       <c r="I64">
         <v>7.2000000000000099</v>
       </c>
-    </row>
-    <row r="65" spans="1:9">
+      <c r="J64" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -2309,8 +2506,11 @@
       <c r="I65">
         <v>7.3000000000000096</v>
       </c>
-    </row>
-    <row r="66" spans="1:9">
+      <c r="J65" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2338,8 +2538,11 @@
       <c r="I66">
         <v>7.4000000000000101</v>
       </c>
-    </row>
-    <row r="67" spans="1:9">
+      <c r="J66" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
       <c r="A67">
         <v>66</v>
       </c>
@@ -2367,8 +2570,11 @@
       <c r="I67">
         <v>7.5000000000000098</v>
       </c>
-    </row>
-    <row r="68" spans="1:9">
+      <c r="J67" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2396,8 +2602,11 @@
       <c r="I68">
         <v>7.6000000000000103</v>
       </c>
-    </row>
-    <row r="69" spans="1:9">
+      <c r="J68" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -2425,8 +2634,11 @@
       <c r="I69">
         <v>7.7000000000000099</v>
       </c>
-    </row>
-    <row r="70" spans="1:9">
+      <c r="J69" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
       <c r="A70">
         <v>69</v>
       </c>
@@ -2454,8 +2666,11 @@
       <c r="I70">
         <v>7.8000000000000096</v>
       </c>
-    </row>
-    <row r="71" spans="1:9">
+      <c r="J70" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2483,8 +2698,11 @@
       <c r="I71">
         <v>7.9000000000000101</v>
       </c>
-    </row>
-    <row r="72" spans="1:9">
+      <c r="J71" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -2512,8 +2730,11 @@
       <c r="I72">
         <v>8.0000000000000107</v>
       </c>
-    </row>
-    <row r="73" spans="1:9">
+      <c r="J72" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
       <c r="A73">
         <v>72</v>
       </c>
@@ -2541,8 +2762,11 @@
       <c r="I73">
         <v>8.1000000000000103</v>
       </c>
-    </row>
-    <row r="74" spans="1:9">
+      <c r="J73" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
       <c r="A74">
         <v>73</v>
       </c>
@@ -2570,8 +2794,11 @@
       <c r="I74">
         <v>8.2000000000000099</v>
       </c>
-    </row>
-    <row r="75" spans="1:9">
+      <c r="J74" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -2599,8 +2826,11 @@
       <c r="I75">
         <v>8.3000000000000096</v>
       </c>
-    </row>
-    <row r="76" spans="1:9">
+      <c r="J75" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
       <c r="A76">
         <v>75</v>
       </c>
@@ -2628,8 +2858,11 @@
       <c r="I76">
         <v>8.4000000000000092</v>
       </c>
-    </row>
-    <row r="77" spans="1:9">
+      <c r="J76" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
       <c r="A77">
         <v>76</v>
       </c>
@@ -2657,8 +2890,11 @@
       <c r="I77">
         <v>8.5000000000000107</v>
       </c>
-    </row>
-    <row r="78" spans="1:9">
+      <c r="J77" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -2686,8 +2922,11 @@
       <c r="I78">
         <v>8.6000000000000103</v>
       </c>
-    </row>
-    <row r="79" spans="1:9">
+      <c r="J78" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
       <c r="A79">
         <v>78</v>
       </c>
@@ -2715,8 +2954,11 @@
       <c r="I79">
         <v>8.7000000000000099</v>
       </c>
-    </row>
-    <row r="80" spans="1:9">
+      <c r="J79" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
       <c r="A80">
         <v>79</v>
       </c>
@@ -2744,8 +2986,11 @@
       <c r="I80">
         <v>8.8000000000000096</v>
       </c>
-    </row>
-    <row r="81" spans="1:9">
+      <c r="J80" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -2773,8 +3018,11 @@
       <c r="I81">
         <v>8.9000000000000092</v>
       </c>
-    </row>
-    <row r="82" spans="1:9">
+      <c r="J81" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
       <c r="A82">
         <v>81</v>
       </c>
@@ -2802,8 +3050,11 @@
       <c r="I82">
         <v>9.0000000000000107</v>
       </c>
-    </row>
-    <row r="83" spans="1:9">
+      <c r="J82" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
       <c r="A83">
         <v>82</v>
       </c>
@@ -2831,8 +3082,11 @@
       <c r="I83">
         <v>9.1000000000000103</v>
       </c>
-    </row>
-    <row r="84" spans="1:9">
+      <c r="J83" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -2860,8 +3114,11 @@
       <c r="I84">
         <v>9.2000000000000099</v>
       </c>
-    </row>
-    <row r="85" spans="1:9">
+      <c r="J84" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
       <c r="A85">
         <v>84</v>
       </c>
@@ -2889,8 +3146,11 @@
       <c r="I85">
         <v>9.3000000000000096</v>
       </c>
-    </row>
-    <row r="86" spans="1:9">
+      <c r="J85" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
       <c r="A86">
         <v>85</v>
       </c>
@@ -2918,8 +3178,11 @@
       <c r="I86">
         <v>9.4000000000000092</v>
       </c>
-    </row>
-    <row r="87" spans="1:9">
+      <c r="J86" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -2947,8 +3210,11 @@
       <c r="I87">
         <v>9.5000000000000107</v>
       </c>
-    </row>
-    <row r="88" spans="1:9">
+      <c r="J87" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10">
       <c r="A88">
         <v>87</v>
       </c>
@@ -2976,8 +3242,11 @@
       <c r="I88">
         <v>9.6000000000000103</v>
       </c>
-    </row>
-    <row r="89" spans="1:9">
+      <c r="J88" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10">
       <c r="A89">
         <v>88</v>
       </c>
@@ -3005,8 +3274,11 @@
       <c r="I89">
         <v>9.7000000000000099</v>
       </c>
-    </row>
-    <row r="90" spans="1:9">
+      <c r="J89" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
       <c r="A90">
         <v>89</v>
       </c>
@@ -3034,8 +3306,11 @@
       <c r="I90">
         <v>9.8000000000000096</v>
       </c>
-    </row>
-    <row r="91" spans="1:9">
+      <c r="J90" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -3063,8 +3338,11 @@
       <c r="I91">
         <v>9.9000000000000092</v>
       </c>
-    </row>
-    <row r="92" spans="1:9">
+      <c r="J91" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10">
       <c r="A92">
         <v>91</v>
       </c>
@@ -3092,8 +3370,11 @@
       <c r="I92">
         <v>10</v>
       </c>
-    </row>
-    <row r="93" spans="1:9">
+      <c r="J92" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10">
       <c r="A93">
         <v>92</v>
       </c>
@@ -3121,8 +3402,11 @@
       <c r="I93">
         <v>10.1</v>
       </c>
-    </row>
-    <row r="94" spans="1:9">
+      <c r="J93" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -3150,8 +3434,11 @@
       <c r="I94">
         <v>10.199999999999999</v>
       </c>
-    </row>
-    <row r="95" spans="1:9">
+      <c r="J94" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10">
       <c r="A95">
         <v>94</v>
       </c>
@@ -3179,8 +3466,11 @@
       <c r="I95">
         <v>10.3</v>
       </c>
-    </row>
-    <row r="96" spans="1:9">
+      <c r="J95" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10">
       <c r="A96">
         <v>95</v>
       </c>
@@ -3207,6 +3497,9 @@
       </c>
       <c r="I96">
         <v>10.4</v>
+      </c>
+      <c r="J96" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -3237,6 +3530,9 @@
       <c r="I97">
         <v>10.5</v>
       </c>
+      <c r="J97" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98">
@@ -3266,6 +3562,9 @@
       <c r="I98">
         <v>10.6</v>
       </c>
+      <c r="J98" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="99" spans="1:11">
       <c r="A99">
@@ -3295,6 +3594,9 @@
       <c r="I99">
         <v>10.7</v>
       </c>
+      <c r="J99" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="1">
@@ -3324,6 +3626,9 @@
       <c r="I100">
         <v>10.8</v>
       </c>
+      <c r="J100" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="101" spans="1:11">
       <c r="A101">
@@ -3353,6 +3658,9 @@
       <c r="I101">
         <v>10.9</v>
       </c>
+      <c r="J101" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="102" spans="1:11">
       <c r="A102">
@@ -3382,6 +3690,9 @@
       <c r="I102">
         <v>11</v>
       </c>
+      <c r="J102" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="1">
@@ -3411,6 +3722,9 @@
       <c r="I103">
         <v>11.1</v>
       </c>
+      <c r="J103" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="104" spans="1:11">
       <c r="A104">
@@ -3440,6 +3754,9 @@
       <c r="I104">
         <v>11.2</v>
       </c>
+      <c r="J104" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="105" spans="1:11">
       <c r="A105">
@@ -3469,6 +3786,9 @@
       <c r="I105">
         <v>11.3</v>
       </c>
+      <c r="J105" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="106" spans="1:11">
       <c r="A106" s="1">
@@ -3498,6 +3818,9 @@
       <c r="I106">
         <v>11.4</v>
       </c>
+      <c r="J106" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="107" spans="1:11">
       <c r="A107">
@@ -3527,6 +3850,9 @@
       <c r="I107">
         <v>11.5</v>
       </c>
+      <c r="J107" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="108" spans="1:11">
       <c r="A108">
@@ -3556,6 +3882,9 @@
       <c r="I108">
         <v>11.6</v>
       </c>
+      <c r="J108" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="1">
@@ -3585,6 +3914,9 @@
       <c r="I109">
         <v>11.7</v>
       </c>
+      <c r="J109" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="110" spans="1:11">
       <c r="A110">
@@ -3614,6 +3946,9 @@
       <c r="I110">
         <v>11.8</v>
       </c>
+      <c r="J110" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="111" spans="1:11">
       <c r="A111">
@@ -3643,6 +3978,9 @@
       <c r="I111">
         <v>11.9</v>
       </c>
+      <c r="J111" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="112" spans="1:11">
       <c r="A112">
@@ -3672,9 +4010,12 @@
       <c r="I112">
         <v>12</v>
       </c>
+      <c r="J112" s="2">
+        <v>2</v>
+      </c>
       <c r="K112" s="3"/>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:10">
       <c r="A113" s="1">
         <v>112</v>
       </c>
@@ -3702,8 +4043,11 @@
       <c r="I113">
         <v>12.1</v>
       </c>
-    </row>
-    <row r="114" spans="1:9">
+      <c r="J113" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10">
       <c r="A114">
         <v>113</v>
       </c>
@@ -3731,8 +4075,11 @@
       <c r="I114">
         <v>12.2</v>
       </c>
-    </row>
-    <row r="115" spans="1:9">
+      <c r="J114" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10">
       <c r="A115">
         <v>114</v>
       </c>
@@ -3760,8 +4107,11 @@
       <c r="I115">
         <v>12.3</v>
       </c>
-    </row>
-    <row r="116" spans="1:9">
+      <c r="J115" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10">
       <c r="A116" s="1">
         <v>115</v>
       </c>
@@ -3789,8 +4139,11 @@
       <c r="I116">
         <v>12.4</v>
       </c>
-    </row>
-    <row r="117" spans="1:9">
+      <c r="J116" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10">
       <c r="A117">
         <v>116</v>
       </c>
@@ -3818,8 +4171,11 @@
       <c r="I117">
         <v>12.5</v>
       </c>
-    </row>
-    <row r="118" spans="1:9">
+      <c r="J117" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10">
       <c r="A118">
         <v>117</v>
       </c>
@@ -3847,8 +4203,11 @@
       <c r="I118">
         <v>12.6</v>
       </c>
-    </row>
-    <row r="119" spans="1:9">
+      <c r="J118" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10">
       <c r="A119" s="1">
         <v>118</v>
       </c>
@@ -3876,8 +4235,11 @@
       <c r="I119">
         <v>12.7</v>
       </c>
-    </row>
-    <row r="120" spans="1:9">
+      <c r="J119" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10">
       <c r="A120">
         <v>119</v>
       </c>
@@ -3905,8 +4267,11 @@
       <c r="I120">
         <v>12.8</v>
       </c>
-    </row>
-    <row r="121" spans="1:9">
+      <c r="J120" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10">
       <c r="A121">
         <v>120</v>
       </c>
@@ -3933,6 +4298,9 @@
       </c>
       <c r="I121">
         <v>12.9</v>
+      </c>
+      <c r="J121" s="2">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4682,10 +5050,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DBDF95B-BB9F-4638-9058-846CC92DE057}">
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:I121"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="9" max="9" width="22.625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4710,8 +5081,11 @@
       <c r="H1" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4736,8 +5110,11 @@
       <c r="H2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -4762,8 +5139,11 @@
       <c r="H3">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4788,8 +5168,11 @@
       <c r="H4">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4814,8 +5197,11 @@
       <c r="H5">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -4840,8 +5226,11 @@
       <c r="H6">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4866,8 +5255,11 @@
       <c r="H7">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4892,8 +5284,11 @@
       <c r="H8">
         <v>1.6</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -4918,8 +5313,11 @@
       <c r="H9">
         <v>1.7</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4944,8 +5342,11 @@
       <c r="H10">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4970,8 +5371,11 @@
       <c r="H11">
         <v>1.9</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -4996,8 +5400,11 @@
       <c r="H12">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5022,8 +5429,11 @@
       <c r="H13">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14">
         <v>13</v>
       </c>
@@ -5048,8 +5458,11 @@
       <c r="H14">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="I14" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -5074,8 +5487,11 @@
       <c r="H15">
         <v>2.2999999999999998</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="I15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16">
         <v>15</v>
       </c>
@@ -5100,8 +5516,11 @@
       <c r="H16">
         <v>2.4</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17">
         <v>16</v>
       </c>
@@ -5126,8 +5545,11 @@
       <c r="H17">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="I17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -5152,8 +5574,11 @@
       <c r="H18">
         <v>2.6</v>
       </c>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="I18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19">
         <v>18</v>
       </c>
@@ -5178,8 +5603,11 @@
       <c r="H19">
         <v>2.7</v>
       </c>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="I19" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20">
         <v>19</v>
       </c>
@@ -5204,8 +5632,11 @@
       <c r="H20">
         <v>2.8</v>
       </c>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="I20" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -5230,8 +5661,11 @@
       <c r="H21">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="I21" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22">
         <v>21</v>
       </c>
@@ -5256,8 +5690,11 @@
       <c r="H22">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="I22" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23">
         <v>22</v>
       </c>
@@ -5282,8 +5719,11 @@
       <c r="H23">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="I23" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24">
         <v>23</v>
       </c>
@@ -5308,8 +5748,11 @@
       <c r="H24">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="I24" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -5334,8 +5777,11 @@
       <c r="H25">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="I25" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26">
         <v>25</v>
       </c>
@@ -5360,8 +5806,11 @@
       <c r="H26">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="27" spans="1:8">
+      <c r="I26" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5386,8 +5835,11 @@
       <c r="H27">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="28" spans="1:8">
+      <c r="I27" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -5412,8 +5864,11 @@
       <c r="H28">
         <v>3.6</v>
       </c>
-    </row>
-    <row r="29" spans="1:8">
+      <c r="I28" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5438,8 +5893,11 @@
       <c r="H29">
         <v>3.7</v>
       </c>
-    </row>
-    <row r="30" spans="1:8">
+      <c r="I29" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5464,8 +5922,11 @@
       <c r="H30">
         <v>3.8</v>
       </c>
-    </row>
-    <row r="31" spans="1:8">
+      <c r="I30" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -5490,8 +5951,11 @@
       <c r="H31">
         <v>3.9</v>
       </c>
-    </row>
-    <row r="32" spans="1:8">
+      <c r="I31" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
     </row>
